--- a/flexforge/docs/generated/FlexForge_Test_Cases_and_Report.xlsx
+++ b/flexforge/docs/generated/FlexForge_Test_Cases_and_Report.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1468,6 +1468,117 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TC-27</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>P1PrimitivesIntegrationTest</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>CRUD is audited</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Create Customer; GET /__audit</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>create entry recorded with user/op</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>TC-28</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>P1PrimitivesIntegrationTest</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Idempotency prevents duplicate create</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>POST Product twice with same Idempotency-Key</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>replay returns same record (HTTP 200)</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TC-29</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>P1PrimitivesIntegrationTest</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>AI step (stub) + notify step</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>POST /flows/assist/run</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>summary returned; notification recorded</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1479,7 +1590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1549,7 +1660,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -1559,7 +1670,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -1604,7 +1715,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -1624,7 +1735,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -1723,30 +1834,40 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RealtimeIntegrationTest</t>
+          <t>P1PrimitivesIntegrationTest</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RelationsIntegrationTest</t>
+          <t>RealtimeIntegrationTest</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>RelationsIntegrationTest</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>SecurityIntegrationTest</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B29" t="n">
         <v>3</v>
       </c>
     </row>
